--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Documents\GITHUB\3D-Display\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Documents\Altium\3D-Display\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A8CAC5C-9F7C-43B8-803B-8BB8B79F8E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10330E0-592F-4F79-8972-688BCFB0D29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="381">
   <si>
     <t>Best.</t>
   </si>
@@ -587,9 +587,6 @@
     <t>RES 13.7K OHM 1/8W .1% SMD 0805</t>
   </si>
   <si>
-    <t>CAP 0.01uF 250V X7R 10% 0805 T/R</t>
-  </si>
-  <si>
     <t>CAP CER  0.1UF 25V X7R 0603</t>
   </si>
   <si>
@@ -731,12 +728,6 @@
     <t>CAP CER 0.01uF</t>
   </si>
   <si>
-    <t>603-C0805KKX7RYBB104</t>
-  </si>
-  <si>
-    <t>https://mou.sr/4wwecmS</t>
-  </si>
-  <si>
     <t>CAP CER 2.2uF</t>
   </si>
   <si>
@@ -920,12 +911,6 @@
     <t>https://mou.sr/4fgtJR1</t>
   </si>
   <si>
-    <t>81-GRM21BR61E106MA3L</t>
-  </si>
-  <si>
-    <t>https://mou.sr/4vAmZUk</t>
-  </si>
-  <si>
     <t>https://mou.sr/4bgyqZO</t>
   </si>
   <si>
@@ -1200,6 +1185,12 @@
   </si>
   <si>
     <t>Strommesswiderstand</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4hMsGJZ</t>
+  </si>
+  <si>
+    <t>80-C0805C106K8P</t>
   </si>
 </sst>
 </file>
@@ -1250,12 +1241,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="6"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1263,13 +1248,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -1324,7 +1334,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1362,22 +1372,20 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -1661,7 +1669,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7.73046875" bestFit="1" customWidth="1"/>
@@ -1669,7 +1677,7 @@
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="19.73046875" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="10.73046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.73046875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.73046875" customWidth="1"/>
     <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.59765625" bestFit="1" customWidth="1"/>
@@ -1682,18 +1690,18 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="G2" s="28"/>
+      <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1705,7 +1713,7 @@
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="10" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1735,28 +1743,28 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>182</v>
+        <v>264</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="G4" s="32">
+      <c r="G4">
         <v>2</v>
       </c>
       <c r="I4" s="14">
         <f>J4*1.2</f>
         <v>0.156</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="14">
         <v>0.13</v>
       </c>
       <c r="K4" s="14">
@@ -1772,28 +1780,28 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>181</v>
+        <v>261</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="G5" s="32">
+      <c r="G5">
         <v>8</v>
       </c>
       <c r="I5" s="14">
         <f t="shared" ref="I5:I28" si="0">J5*1.2</f>
         <v>0.84</v>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="14">
         <v>0.7</v>
       </c>
       <c r="K5" s="14">
@@ -1809,28 +1817,28 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>226</v>
+        <v>261</v>
+      </c>
+      <c r="C6" t="s">
+        <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>225</v>
+        <v>185</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>224</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="G6" s="32">
+        <v>223</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="I6" s="14">
         <f t="shared" si="0"/>
         <v>0.20400000000000001</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="14">
         <v>0.17</v>
       </c>
       <c r="K6" s="14">
@@ -1845,66 +1853,67 @@
       <c r="N6" s="15"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7" s="31"/>
       <c r="B7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>180</v>
+        <v>261</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E7" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="G7" s="32">
-        <v>3</v>
+      <c r="G7">
+        <v>4</v>
       </c>
       <c r="I7" s="14">
         <f t="shared" si="0"/>
         <v>0.108</v>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="14">
         <v>0.09</v>
       </c>
       <c r="K7" s="14">
         <f t="shared" si="1"/>
-        <v>0.32400000000000001</v>
+        <v>0.432</v>
       </c>
       <c r="L7" s="24">
         <f t="shared" si="2"/>
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="15"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E8" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G8" s="32">
+      <c r="G8">
         <v>2</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="0"/>
         <v>0.192</v>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="14">
         <v>0.16</v>
       </c>
       <c r="K8" s="14">
@@ -1920,28 +1929,28 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E9" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="F9" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="G9" s="32">
+      <c r="G9">
         <v>1</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="14">
         <v>0.1</v>
       </c>
       <c r="K9" s="14">
@@ -1957,28 +1966,28 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>229</v>
+        <v>261</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>226</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>231</v>
+        <v>185</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>228</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="G10" s="32">
+        <v>227</v>
+      </c>
+      <c r="G10">
         <v>2</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" si="0"/>
         <v>1.1279999999999999</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="14">
         <v>0.94</v>
       </c>
       <c r="K10" s="14">
@@ -1993,66 +2002,45 @@
       <c r="N10" s="15"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
-        <v>264</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="G11" s="32">
-        <v>1</v>
-      </c>
-      <c r="I11" s="14">
-        <f t="shared" si="0"/>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="J11" s="35">
-        <v>0.11</v>
-      </c>
-      <c r="K11" s="14">
-        <f t="shared" si="1"/>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="L11" s="24">
-        <f t="shared" si="2"/>
-        <v>0.11</v>
-      </c>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="37"/>
       <c r="M11" s="16"/>
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="G12" s="32">
+      <c r="G12">
         <v>4</v>
       </c>
       <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>1.8959999999999999</v>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="14">
         <v>1.58</v>
       </c>
       <c r="K12" s="14">
@@ -2068,28 +2056,28 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>264</v>
-      </c>
-      <c r="C13" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="D13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" s="31" t="s">
+      <c r="F13" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="F13" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="G13" s="32">
+      <c r="G13">
         <v>1</v>
       </c>
       <c r="I13" s="14">
         <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="14">
         <v>0.6</v>
       </c>
       <c r="K13" s="14">
@@ -2105,28 +2093,28 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>223</v>
+        <v>261</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E14" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F14" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F14" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="G14" s="32">
+      <c r="G14">
         <v>2</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="0"/>
         <v>1.8839999999999999</v>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="14">
         <v>1.57</v>
       </c>
       <c r="K14" s="14">
@@ -2142,28 +2130,28 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>189</v>
+        <v>261</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
-      </c>
-      <c r="E15" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="F15" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="G15" s="32">
+      <c r="G15">
         <v>3</v>
       </c>
       <c r="I15" s="14">
         <f t="shared" si="0"/>
         <v>2.2320000000000002</v>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="14">
         <v>1.86</v>
       </c>
       <c r="K15" s="14">
@@ -2179,28 +2167,28 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>198</v>
+        <v>261</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>197</v>
       </c>
       <c r="D16" t="s">
-        <v>186</v>
-      </c>
-      <c r="E16" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="G16" s="32">
+      <c r="G16">
         <v>2</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" si="0"/>
         <v>1.0920000000000001</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="14">
         <v>0.91</v>
       </c>
       <c r="K16" s="14">
@@ -2216,28 +2204,28 @@
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>264</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>197</v>
+        <v>261</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>196</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
-      </c>
-      <c r="E17" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="F17" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="G17" s="32">
+      <c r="G17">
         <v>2</v>
       </c>
       <c r="I17" s="14">
         <f t="shared" si="0"/>
         <v>0.85199999999999998</v>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="14">
         <v>0.71</v>
       </c>
       <c r="K17" s="14">
@@ -2253,28 +2241,28 @@
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>264</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>183</v>
+        <v>261</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>182</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
-      </c>
-      <c r="E18" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F18" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="G18" s="32">
+      <c r="G18">
         <v>1</v>
       </c>
       <c r="I18" s="14">
         <f t="shared" si="0"/>
         <v>0.13200000000000001</v>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="14">
         <v>0.11</v>
       </c>
       <c r="K18" s="14">
@@ -2290,28 +2278,28 @@
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>264</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>184</v>
+        <v>261</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>183</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
-      </c>
-      <c r="E19" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="G19" s="32">
+      <c r="G19">
         <v>1</v>
       </c>
       <c r="I19" s="14">
         <f t="shared" si="0"/>
         <v>0.13200000000000001</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="14">
         <v>0.11</v>
       </c>
       <c r="K19" s="14">
@@ -2327,28 +2315,28 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>264</v>
-      </c>
-      <c r="C20" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="D20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E20" s="31" t="s">
+      <c r="F20" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="F20" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="G20" s="32">
+      <c r="G20">
         <v>2</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" si="0"/>
         <v>3.0960000000000001</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="14">
         <v>2.58</v>
       </c>
       <c r="K20" s="14">
@@ -2364,28 +2352,28 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>264</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>232</v>
+        <v>261</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>229</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>234</v>
+        <v>185</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>231</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="G21" s="32">
+        <v>230</v>
+      </c>
+      <c r="G21">
         <v>2</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" si="0"/>
         <v>0.49199999999999994</v>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="14">
         <v>0.41</v>
       </c>
       <c r="K21" s="14">
@@ -2401,28 +2389,28 @@
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>264</v>
-      </c>
-      <c r="C22" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" t="s">
+        <v>185</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="D22" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G22" s="32">
+      <c r="G22">
         <v>1</v>
       </c>
       <c r="I22" s="14">
         <f t="shared" si="0"/>
         <v>0.108</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="14">
         <v>0.09</v>
       </c>
       <c r="K22" s="14">
@@ -2438,28 +2426,28 @@
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>264</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>244</v>
+        <v>261</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>241</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>245</v>
+        <v>185</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>242</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G23" s="32">
+        <v>243</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" si="0"/>
         <v>0.108</v>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="14">
         <v>0.09</v>
       </c>
       <c r="K23" s="14">
@@ -2475,28 +2463,28 @@
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>264</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>247</v>
+        <v>261</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>244</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>248</v>
+        <v>185</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="G24" s="32">
+        <v>246</v>
+      </c>
+      <c r="G24">
         <v>8</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" si="0"/>
         <v>0.108</v>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="14">
         <v>0.09</v>
       </c>
       <c r="K24" s="14">
@@ -2512,28 +2500,28 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>264</v>
-      </c>
-      <c r="C25" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="27" t="s">
         <v>178</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>239</v>
+        <v>185</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>236</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="G25" s="32">
+        <v>237</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
       <c r="I25" s="14">
         <f t="shared" si="0"/>
         <v>0.108</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="14">
         <v>0.09</v>
       </c>
       <c r="K25" s="14">
@@ -2549,28 +2537,28 @@
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C26" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="D26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E26" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="D26" t="s">
-        <v>186</v>
-      </c>
-      <c r="E26" s="31" t="s">
+      <c r="F26" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="F26" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="G26" s="32">
+      <c r="G26">
         <v>1</v>
       </c>
       <c r="I26" s="14">
         <f t="shared" si="0"/>
         <v>6.48</v>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="14">
         <v>5.4</v>
       </c>
       <c r="K26" s="14">
@@ -2586,28 +2574,28 @@
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>264</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>243</v>
+        <v>261</v>
+      </c>
+      <c r="C27" t="s">
+        <v>240</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>241</v>
+        <v>185</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>238</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="G27" s="37">
+        <v>239</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
       <c r="I27" s="14">
         <f t="shared" si="0"/>
         <v>3.1799999999999997</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="14">
         <v>2.65</v>
       </c>
       <c r="K27" s="14">
@@ -2623,21 +2611,21 @@
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>265</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>252</v>
+        <v>262</v>
+      </c>
+      <c r="C28" t="s">
+        <v>249</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>250</v>
+        <v>185</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>247</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G28" s="27">
+        <v>248</v>
+      </c>
+      <c r="G28">
         <v>48</v>
       </c>
       <c r="I28" s="14">
@@ -2660,21 +2648,21 @@
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>265</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>255</v>
+        <v>262</v>
+      </c>
+      <c r="C29" t="s">
+        <v>252</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>253</v>
+        <v>185</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>250</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G29" s="27">
+        <v>251</v>
+      </c>
+      <c r="G29">
         <v>1</v>
       </c>
       <c r="I29" s="14">
@@ -2694,25 +2682,25 @@
       </c>
       <c r="M29" s="16"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="38"/>
+      <c r="O29" s="28"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D30" t="s">
-        <v>257</v>
-      </c>
-      <c r="E30" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="G30" s="27">
+      <c r="G30">
         <v>2</v>
       </c>
       <c r="I30" s="14">
@@ -2733,26 +2721,26 @@
       <c r="M30" s="16"/>
       <c r="N30" s="15"/>
       <c r="O30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E31" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>261</v>
-      </c>
-      <c r="G31" s="27">
+        <v>185</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31">
         <v>10</v>
       </c>
       <c r="I31" s="14">
@@ -2775,21 +2763,21 @@
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" t="s">
+        <v>266</v>
+      </c>
+      <c r="D32" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F32" t="s">
         <v>268</v>
       </c>
-      <c r="C32" t="s">
-        <v>269</v>
-      </c>
-      <c r="D32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="F32" t="s">
-        <v>271</v>
-      </c>
-      <c r="G32" s="27">
+      <c r="G32">
         <v>1</v>
       </c>
       <c r="I32" s="14">
@@ -2810,23 +2798,23 @@
       <c r="M32" s="16"/>
       <c r="N32" s="15"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
-      </c>
-      <c r="E33" s="31" t="s">
-        <v>272</v>
+        <v>185</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>269</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="G33" s="27">
+        <v>270</v>
+      </c>
+      <c r="G33">
         <v>11</v>
       </c>
       <c r="I33" s="14">
@@ -2847,60 +2835,60 @@
       <c r="M33" s="16"/>
       <c r="N33" s="15"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>274</v>
+        <v>185</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>271</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="G34" s="27">
+        <v>272</v>
+      </c>
+      <c r="G34">
         <v>2</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" ref="I34:I74" si="3">J34*1.2</f>
+        <f t="shared" ref="I34:I75" si="3">J34*1.2</f>
         <v>0.68399999999999994</v>
       </c>
       <c r="J34" s="24">
         <v>0.56999999999999995</v>
       </c>
       <c r="K34" s="14">
-        <f t="shared" ref="K34:K74" si="4">I34*G34</f>
+        <f t="shared" ref="K34:K75" si="4">I34*G34</f>
         <v>1.3679999999999999</v>
       </c>
       <c r="L34" s="24">
-        <f t="shared" ref="L34:L74" si="5">J34*G34</f>
+        <f t="shared" ref="L34:L75" si="5">J34*G34</f>
         <v>1.1399999999999999</v>
       </c>
       <c r="M34" s="16"/>
       <c r="N34" s="15"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C35" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" s="31" t="s">
-        <v>277</v>
+        <v>185</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>274</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G35" s="27">
+        <v>276</v>
+      </c>
+      <c r="G35">
         <v>2</v>
       </c>
       <c r="I35" s="14">
@@ -2921,23 +2909,23 @@
       <c r="M35" s="16"/>
       <c r="N35" s="15"/>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C36" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D36" t="s">
-        <v>186</v>
-      </c>
-      <c r="E36" s="31" t="s">
-        <v>280</v>
+        <v>185</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>277</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G36" s="27">
+        <v>278</v>
+      </c>
+      <c r="G36">
         <v>4</v>
       </c>
       <c r="I36" s="14">
@@ -2958,23 +2946,23 @@
       <c r="M36" s="16"/>
       <c r="N36" s="15"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C37" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
-      </c>
-      <c r="E37" s="31" t="s">
-        <v>283</v>
+        <v>185</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>280</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="G37" s="27">
+        <v>281</v>
+      </c>
+      <c r="G37">
         <v>1</v>
       </c>
       <c r="I37" s="14">
@@ -2995,23 +2983,23 @@
       <c r="M37" s="16"/>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C38" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E38" s="31" t="s">
-        <v>287</v>
+        <v>185</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>284</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="G38" s="27">
+        <v>285</v>
+      </c>
+      <c r="G38">
         <v>3</v>
       </c>
       <c r="I38" s="14">
@@ -3032,23 +3020,23 @@
       <c r="M38" s="16"/>
       <c r="N38" s="15"/>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>268</v>
-      </c>
-      <c r="C39" s="34" t="s">
-        <v>252</v>
+        <v>265</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>249</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
-      </c>
-      <c r="E39" s="31" t="s">
-        <v>210</v>
+        <v>185</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>209</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="G39" s="27">
+        <v>286</v>
+      </c>
+      <c r="G39">
         <v>2</v>
       </c>
       <c r="I39" s="14">
@@ -3069,1022 +3057,1003 @@
       <c r="M39" s="16"/>
       <c r="N39" s="15"/>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A40" s="31"/>
       <c r="B40" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C40" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D40" t="s">
-        <v>186</v>
-      </c>
-      <c r="E40" s="31" t="s">
-        <v>290</v>
+        <v>185</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>380</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="G40" s="27">
+        <v>379</v>
+      </c>
+      <c r="G40">
         <v>3</v>
       </c>
       <c r="I40" s="14">
         <f t="shared" si="3"/>
-        <v>0.16800000000000001</v>
+        <v>0.20639999999999997</v>
       </c>
       <c r="J40" s="24">
-        <v>0.14000000000000001</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="K40" s="14">
         <f t="shared" si="4"/>
-        <v>0.504</v>
+        <v>0.61919999999999997</v>
       </c>
       <c r="L40" s="24">
         <f t="shared" si="5"/>
-        <v>0.42000000000000004</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="M40" s="16"/>
       <c r="N40" s="15"/>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B41" t="s">
-        <v>268</v>
-      </c>
-      <c r="C41" t="s">
-        <v>229</v>
-      </c>
-      <c r="D41" t="s">
-        <v>186</v>
-      </c>
-      <c r="E41" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="G41" s="27">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A41" s="38"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="37"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="15"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>265</v>
+      </c>
+      <c r="C42" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="G42">
         <v>2</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I42" s="14">
         <f t="shared" si="3"/>
         <v>1.1279999999999999</v>
       </c>
-      <c r="J41" s="24">
+      <c r="J42" s="24">
         <v>0.94</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K42" s="14">
         <f t="shared" si="4"/>
         <v>2.2559999999999998</v>
       </c>
-      <c r="L41" s="24">
+      <c r="L42" s="24">
         <f t="shared" si="5"/>
         <v>1.88</v>
       </c>
-      <c r="M41" s="16"/>
-      <c r="N41" s="15"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B42" t="s">
-        <v>268</v>
-      </c>
-      <c r="C42" t="s">
-        <v>295</v>
-      </c>
-      <c r="D42" t="s">
-        <v>186</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="G42" s="27">
+      <c r="M42" s="16"/>
+      <c r="N42" s="15"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>265</v>
+      </c>
+      <c r="C43" t="s">
+        <v>290</v>
+      </c>
+      <c r="D43" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="G43">
         <v>2</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I43" s="14">
         <f t="shared" si="3"/>
         <v>0.40800000000000003</v>
       </c>
-      <c r="J42" s="24">
+      <c r="J43" s="24">
         <v>0.34</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K43" s="14">
         <f t="shared" si="4"/>
         <v>0.81600000000000006</v>
       </c>
-      <c r="L42" s="24">
+      <c r="L43" s="24">
         <f t="shared" si="5"/>
         <v>0.68</v>
       </c>
-      <c r="M42" s="16"/>
-      <c r="N42" s="15"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B43" t="s">
-        <v>268</v>
-      </c>
-      <c r="C43" t="s">
-        <v>297</v>
-      </c>
-      <c r="D43" t="s">
-        <v>186</v>
-      </c>
-      <c r="E43" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="G43" s="27">
+      <c r="M43" s="16"/>
+      <c r="N43" s="15"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" t="s">
+        <v>292</v>
+      </c>
+      <c r="D44" t="s">
+        <v>185</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G44">
         <v>1</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I44" s="14">
         <f t="shared" si="3"/>
         <v>3.7199999999999998</v>
       </c>
-      <c r="J43" s="14">
+      <c r="J44" s="14">
         <v>3.1</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K44" s="14">
         <f t="shared" si="4"/>
         <v>3.7199999999999998</v>
       </c>
-      <c r="L43" s="24">
+      <c r="L44" s="24">
         <f t="shared" si="5"/>
         <v>3.1</v>
       </c>
-      <c r="M43" s="16"/>
-      <c r="N43" s="15"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
-        <v>268</v>
-      </c>
-      <c r="C44" t="s">
-        <v>301</v>
-      </c>
-      <c r="D44" t="s">
-        <v>186</v>
-      </c>
-      <c r="E44" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="G44" s="27">
+      <c r="M44" s="16"/>
+      <c r="N44" s="15"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>265</v>
+      </c>
+      <c r="C45" t="s">
+        <v>296</v>
+      </c>
+      <c r="D45" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G45">
         <v>1</v>
       </c>
-      <c r="I44" s="14">
+      <c r="I45" s="14">
         <f t="shared" si="3"/>
         <v>1.728</v>
       </c>
-      <c r="J44" s="14">
+      <c r="J45" s="14">
         <v>1.44</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K45" s="14">
         <f t="shared" si="4"/>
         <v>1.728</v>
       </c>
-      <c r="L44" s="24">
+      <c r="L45" s="24">
         <f t="shared" si="5"/>
         <v>1.44</v>
       </c>
-      <c r="M44" s="16"/>
-      <c r="N44" s="15"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>268</v>
-      </c>
-      <c r="C45" t="s">
-        <v>304</v>
-      </c>
-      <c r="D45" t="s">
-        <v>186</v>
-      </c>
-      <c r="E45" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="G45" s="27">
+      <c r="M45" s="16"/>
+      <c r="N45" s="15"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" t="s">
+        <v>299</v>
+      </c>
+      <c r="D46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G46">
         <v>2</v>
       </c>
-      <c r="I45" s="14">
+      <c r="I46" s="14">
         <f t="shared" si="3"/>
         <v>0.42</v>
       </c>
-      <c r="J45" s="14">
+      <c r="J46" s="14">
         <v>0.35</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K46" s="14">
         <f t="shared" si="4"/>
         <v>0.84</v>
       </c>
-      <c r="L45" s="24">
+      <c r="L46" s="24">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="M45" s="16"/>
-      <c r="N45" s="15"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>268</v>
-      </c>
-      <c r="C46" t="s">
-        <v>306</v>
-      </c>
-      <c r="D46" t="s">
-        <v>186</v>
-      </c>
-      <c r="E46" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="G46" s="27">
+      <c r="M46" s="16"/>
+      <c r="N46" s="15"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" t="s">
+        <v>301</v>
+      </c>
+      <c r="D47" t="s">
+        <v>185</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="G47">
         <v>1</v>
       </c>
-      <c r="I46" s="14">
+      <c r="I47" s="14">
         <f t="shared" si="3"/>
         <v>6.3119999999999994</v>
       </c>
-      <c r="J46" s="14">
+      <c r="J47" s="14">
         <v>5.26</v>
       </c>
-      <c r="K46" s="14">
+      <c r="K47" s="14">
         <f t="shared" si="4"/>
         <v>6.3119999999999994</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L47" s="24">
         <f t="shared" si="5"/>
         <v>5.26</v>
       </c>
-      <c r="M46" s="16"/>
-      <c r="N46" s="15"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>268</v>
-      </c>
-      <c r="C47" t="s">
-        <v>309</v>
-      </c>
-      <c r="D47" t="s">
-        <v>186</v>
-      </c>
-      <c r="E47" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="G47" s="27">
+      <c r="M47" s="16"/>
+      <c r="N47" s="15"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" t="s">
+        <v>304</v>
+      </c>
+      <c r="D48" t="s">
+        <v>185</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="G48">
         <v>1</v>
       </c>
-      <c r="I47" s="14">
+      <c r="I48" s="14">
         <f t="shared" si="3"/>
         <v>0.70799999999999996</v>
       </c>
-      <c r="J47" s="14">
+      <c r="J48" s="14">
         <v>0.59</v>
       </c>
-      <c r="K47" s="14">
+      <c r="K48" s="14">
         <f t="shared" si="4"/>
         <v>0.70799999999999996</v>
       </c>
-      <c r="L47" s="24">
+      <c r="L48" s="24">
         <f t="shared" si="5"/>
         <v>0.59</v>
       </c>
-      <c r="M47" s="16"/>
-      <c r="N47" s="15"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>268</v>
-      </c>
-      <c r="C48" t="s">
-        <v>311</v>
-      </c>
-      <c r="D48" t="s">
-        <v>186</v>
-      </c>
-      <c r="E48" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="G48" s="27">
+      <c r="M48" s="16"/>
+      <c r="N48" s="15"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>265</v>
+      </c>
+      <c r="C49" t="s">
+        <v>306</v>
+      </c>
+      <c r="D49" t="s">
+        <v>185</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="G49">
         <v>1</v>
       </c>
-      <c r="I48" s="14">
+      <c r="I49" s="14">
         <f t="shared" si="3"/>
         <v>0.72</v>
       </c>
-      <c r="J48" s="14">
+      <c r="J49" s="14">
         <v>0.6</v>
       </c>
-      <c r="K48" s="14">
+      <c r="K49" s="14">
         <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
-      <c r="L48" s="24">
+      <c r="L49" s="24">
         <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
-      <c r="M48" s="16"/>
-      <c r="N48" s="15"/>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B49" t="s">
-        <v>268</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="M49" s="16"/>
+      <c r="N49" s="15"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>265</v>
+      </c>
+      <c r="C50" t="s">
         <v>177</v>
       </c>
-      <c r="D49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E49" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="G49" s="27">
+      <c r="D50" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="G50">
         <v>2</v>
       </c>
-      <c r="I49" s="14">
+      <c r="I50" s="14">
         <f t="shared" si="3"/>
         <v>2.1</v>
       </c>
-      <c r="J49" s="14">
+      <c r="J50" s="14">
         <v>1.75</v>
       </c>
-      <c r="K49" s="14">
+      <c r="K50" s="14">
         <f t="shared" si="4"/>
         <v>4.2</v>
       </c>
-      <c r="L49" s="24">
+      <c r="L50" s="24">
         <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
-      <c r="M49" s="16"/>
-      <c r="N49" s="15"/>
-    </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
-        <v>268</v>
-      </c>
-      <c r="C50" t="s">
-        <v>314</v>
-      </c>
-      <c r="D50" t="s">
-        <v>186</v>
-      </c>
-      <c r="E50" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="G50" s="27">
+      <c r="M50" s="16"/>
+      <c r="N50" s="15"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>265</v>
+      </c>
+      <c r="C51" t="s">
+        <v>309</v>
+      </c>
+      <c r="D51" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G51">
         <v>1</v>
       </c>
-      <c r="I50" s="14">
+      <c r="I51" s="14">
         <f t="shared" si="3"/>
         <v>0.93599999999999994</v>
       </c>
-      <c r="J50" s="14">
+      <c r="J51" s="14">
         <v>0.78</v>
       </c>
-      <c r="K50" s="14">
+      <c r="K51" s="14">
         <f t="shared" si="4"/>
         <v>0.93599999999999994</v>
       </c>
-      <c r="L50" s="24">
+      <c r="L51" s="24">
         <f t="shared" si="5"/>
         <v>0.78</v>
       </c>
-      <c r="M50" s="16"/>
-      <c r="N50" s="15"/>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>268</v>
-      </c>
-      <c r="C51" t="s">
-        <v>319</v>
-      </c>
-      <c r="D51" t="s">
-        <v>186</v>
-      </c>
-      <c r="E51" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="G51" s="27">
+      <c r="M51" s="16"/>
+      <c r="N51" s="15"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>265</v>
+      </c>
+      <c r="C52" t="s">
+        <v>314</v>
+      </c>
+      <c r="D52" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="G52">
         <v>1</v>
       </c>
-      <c r="I51" s="14">
+      <c r="I52" s="14">
         <f t="shared" si="3"/>
         <v>2.8919999999999999</v>
       </c>
-      <c r="J51" s="14">
+      <c r="J52" s="14">
         <v>2.41</v>
       </c>
-      <c r="K51" s="14">
+      <c r="K52" s="14">
         <f t="shared" si="4"/>
         <v>2.8919999999999999</v>
       </c>
-      <c r="L51" s="24">
+      <c r="L52" s="24">
         <f t="shared" si="5"/>
         <v>2.41</v>
       </c>
-      <c r="M51" s="16"/>
-      <c r="N51" s="15"/>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>268</v>
-      </c>
-      <c r="C52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D52" t="s">
-        <v>186</v>
-      </c>
-      <c r="E52" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="G52" s="27">
+      <c r="M52" s="16"/>
+      <c r="N52" s="15"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>265</v>
+      </c>
+      <c r="C53" t="s">
+        <v>317</v>
+      </c>
+      <c r="D53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="G53">
         <v>1</v>
       </c>
-      <c r="I52" s="14">
+      <c r="I53" s="14">
         <f t="shared" si="3"/>
         <v>0.54</v>
       </c>
-      <c r="J52" s="14">
+      <c r="J53" s="14">
         <v>0.45</v>
       </c>
-      <c r="K52" s="14">
+      <c r="K53" s="14">
         <f t="shared" si="4"/>
         <v>0.54</v>
       </c>
-      <c r="L52" s="24">
+      <c r="L53" s="24">
         <f t="shared" si="5"/>
         <v>0.45</v>
       </c>
-      <c r="M52" s="16"/>
-      <c r="N52" s="15"/>
-    </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>268</v>
-      </c>
-      <c r="C53" t="s">
-        <v>325</v>
-      </c>
-      <c r="D53" t="s">
-        <v>186</v>
-      </c>
-      <c r="E53" s="31" t="s">
-        <v>323</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="G53" s="27">
+      <c r="M53" s="16"/>
+      <c r="N53" s="15"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" t="s">
+        <v>320</v>
+      </c>
+      <c r="D54" t="s">
+        <v>185</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="G54">
         <v>2</v>
       </c>
-      <c r="I53" s="14">
+      <c r="I54" s="14">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
-      <c r="J53" s="14">
+      <c r="J54" s="14">
         <v>0.25</v>
       </c>
-      <c r="K53" s="14">
+      <c r="K54" s="14">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="L53" s="24">
+      <c r="L54" s="24">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="M53" s="16"/>
-      <c r="N53" s="15"/>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>268</v>
-      </c>
-      <c r="C54" t="s">
-        <v>328</v>
-      </c>
-      <c r="D54" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="G54" s="27">
+      <c r="M54" s="16"/>
+      <c r="N54" s="15"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" t="s">
+        <v>323</v>
+      </c>
+      <c r="D55" t="s">
+        <v>185</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="G55">
         <v>1</v>
       </c>
-      <c r="I54" s="14">
+      <c r="I55" s="14">
         <f t="shared" si="3"/>
         <v>1.452</v>
       </c>
-      <c r="J54" s="14">
+      <c r="J55" s="14">
         <v>1.21</v>
       </c>
-      <c r="K54" s="14">
+      <c r="K55" s="14">
         <f t="shared" si="4"/>
         <v>1.452</v>
       </c>
-      <c r="L54" s="24">
+      <c r="L55" s="24">
         <f t="shared" si="5"/>
         <v>1.21</v>
       </c>
-      <c r="M54" s="16"/>
-      <c r="N54" s="15"/>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>268</v>
-      </c>
-      <c r="C55" t="s">
-        <v>244</v>
-      </c>
-      <c r="D55" t="s">
-        <v>186</v>
-      </c>
-      <c r="E55" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="G55" s="27">
+      <c r="M55" s="16"/>
+      <c r="N55" s="15"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>265</v>
+      </c>
+      <c r="C56" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" t="s">
+        <v>185</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="G56">
         <v>2</v>
       </c>
-      <c r="I55" s="14">
+      <c r="I56" s="14">
         <f t="shared" si="3"/>
         <v>1.1279999999999999</v>
       </c>
-      <c r="J55" s="14">
+      <c r="J56" s="14">
         <v>0.94</v>
       </c>
-      <c r="K55" s="14">
+      <c r="K56" s="14">
         <f t="shared" si="4"/>
         <v>2.2559999999999998</v>
       </c>
-      <c r="L55" s="24">
+      <c r="L56" s="24">
         <f t="shared" si="5"/>
         <v>1.88</v>
       </c>
-      <c r="M55" s="16"/>
-      <c r="N55" s="15"/>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B56" t="s">
-        <v>268</v>
-      </c>
-      <c r="C56" t="s">
-        <v>232</v>
-      </c>
-      <c r="D56" t="s">
-        <v>186</v>
-      </c>
-      <c r="E56" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="G56" s="27">
+      <c r="M56" s="16"/>
+      <c r="N56" s="15"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>265</v>
+      </c>
+      <c r="C57" t="s">
+        <v>229</v>
+      </c>
+      <c r="D57" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G57">
         <v>3</v>
       </c>
-      <c r="I56" s="14">
+      <c r="I57" s="14">
         <f t="shared" si="3"/>
         <v>0.49199999999999994</v>
       </c>
-      <c r="J56" s="14">
+      <c r="J57" s="14">
         <v>0.41</v>
       </c>
-      <c r="K56" s="14">
+      <c r="K57" s="14">
         <f t="shared" si="4"/>
         <v>1.4759999999999998</v>
       </c>
-      <c r="L56" s="24">
+      <c r="L57" s="24">
         <f t="shared" si="5"/>
         <v>1.23</v>
       </c>
-      <c r="M56" s="16"/>
-      <c r="N56" s="15"/>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>268</v>
-      </c>
-      <c r="C57" t="s">
-        <v>333</v>
-      </c>
-      <c r="D57" t="s">
-        <v>186</v>
-      </c>
-      <c r="E57" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="G57" s="27">
+      <c r="M57" s="16"/>
+      <c r="N57" s="15"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>265</v>
+      </c>
+      <c r="C58" t="s">
+        <v>328</v>
+      </c>
+      <c r="D58" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="G58">
         <v>2</v>
       </c>
-      <c r="I57" s="14">
+      <c r="I58" s="14">
         <f t="shared" si="3"/>
         <v>0.27600000000000002</v>
       </c>
-      <c r="J57" s="14">
+      <c r="J58" s="14">
         <v>0.23</v>
       </c>
-      <c r="K57" s="14">
+      <c r="K58" s="14">
         <f t="shared" si="4"/>
         <v>0.55200000000000005</v>
       </c>
-      <c r="L57" s="24">
+      <c r="L58" s="24">
         <f t="shared" si="5"/>
         <v>0.46</v>
       </c>
-      <c r="M57" s="16"/>
-      <c r="N57" s="15"/>
-    </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>268</v>
-      </c>
-      <c r="C58" t="s">
-        <v>336</v>
-      </c>
-      <c r="D58" t="s">
-        <v>186</v>
-      </c>
-      <c r="E58" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="G58" s="27">
+      <c r="M58" s="16"/>
+      <c r="N58" s="15"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>265</v>
+      </c>
+      <c r="C59" t="s">
+        <v>331</v>
+      </c>
+      <c r="D59" t="s">
+        <v>185</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="G59">
         <v>1</v>
       </c>
-      <c r="I58" s="14">
+      <c r="I59" s="14">
         <f t="shared" si="3"/>
         <v>0.108</v>
       </c>
-      <c r="J58" s="14">
+      <c r="J59" s="14">
         <v>0.09</v>
       </c>
-      <c r="K58" s="14">
+      <c r="K59" s="14">
         <f t="shared" si="4"/>
         <v>0.108</v>
       </c>
-      <c r="L58" s="24">
+      <c r="L59" s="24">
         <f t="shared" si="5"/>
         <v>0.09</v>
       </c>
-      <c r="M58" s="16"/>
-      <c r="N58" s="15"/>
-    </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>268</v>
-      </c>
-      <c r="C59" t="s">
-        <v>339</v>
-      </c>
-      <c r="D59" t="s">
-        <v>186</v>
-      </c>
-      <c r="E59" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="G59" s="27">
+      <c r="M59" s="16"/>
+      <c r="N59" s="15"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>265</v>
+      </c>
+      <c r="C60" t="s">
+        <v>334</v>
+      </c>
+      <c r="D60" t="s">
+        <v>185</v>
+      </c>
+      <c r="E60" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="G60">
         <v>2</v>
       </c>
-      <c r="I59" s="14">
+      <c r="I60" s="14">
         <f t="shared" si="3"/>
         <v>0.13200000000000001</v>
       </c>
-      <c r="J59" s="14">
+      <c r="J60" s="14">
         <v>0.11</v>
       </c>
-      <c r="K59" s="14">
+      <c r="K60" s="14">
         <f t="shared" si="4"/>
         <v>0.26400000000000001</v>
       </c>
-      <c r="L59" s="24">
+      <c r="L60" s="24">
         <f t="shared" si="5"/>
         <v>0.22</v>
       </c>
-      <c r="M59" s="16"/>
-      <c r="N59" s="15"/>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B60" t="s">
-        <v>268</v>
-      </c>
-      <c r="C60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D60" t="s">
-        <v>186</v>
-      </c>
-      <c r="E60" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="G60" s="27">
+      <c r="M60" s="16"/>
+      <c r="N60" s="15"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>265</v>
+      </c>
+      <c r="C61" t="s">
+        <v>337</v>
+      </c>
+      <c r="D61" t="s">
+        <v>185</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="G61">
         <v>1</v>
       </c>
-      <c r="I60" s="14">
+      <c r="I61" s="14">
         <f t="shared" si="3"/>
         <v>0.108</v>
       </c>
-      <c r="J60" s="14">
+      <c r="J61" s="14">
         <v>0.09</v>
       </c>
-      <c r="K60" s="14">
+      <c r="K61" s="14">
         <f t="shared" si="4"/>
         <v>0.108</v>
       </c>
-      <c r="L60" s="24">
+      <c r="L61" s="24">
         <f t="shared" si="5"/>
         <v>0.09</v>
       </c>
-      <c r="M60" s="16"/>
-      <c r="N60" s="15"/>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B61" t="s">
-        <v>268</v>
-      </c>
-      <c r="C61" t="s">
-        <v>345</v>
-      </c>
-      <c r="D61" t="s">
-        <v>186</v>
-      </c>
-      <c r="E61" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="G61" s="27">
+      <c r="M61" s="16"/>
+      <c r="N61" s="15"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>265</v>
+      </c>
+      <c r="C62" t="s">
+        <v>340</v>
+      </c>
+      <c r="D62" t="s">
+        <v>185</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="G62">
         <v>1</v>
       </c>
-      <c r="I61" s="14">
+      <c r="I62" s="14">
         <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
-      <c r="J61" s="14">
+      <c r="J62" s="14">
         <v>0.1</v>
       </c>
-      <c r="K61" s="14">
+      <c r="K62" s="14">
         <f t="shared" si="4"/>
         <v>0.12</v>
       </c>
-      <c r="L61" s="24">
+      <c r="L62" s="24">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="M61" s="16"/>
-      <c r="N61" s="15"/>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B62" t="s">
-        <v>268</v>
-      </c>
-      <c r="C62" t="s">
-        <v>348</v>
-      </c>
-      <c r="D62" t="s">
-        <v>186</v>
-      </c>
-      <c r="E62" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="G62" s="27">
+      <c r="M62" s="16"/>
+      <c r="N62" s="15"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>265</v>
+      </c>
+      <c r="C63" t="s">
+        <v>343</v>
+      </c>
+      <c r="D63" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="G63">
         <v>1</v>
       </c>
-      <c r="I62" s="14">
+      <c r="I63" s="14">
         <f t="shared" si="3"/>
         <v>0.40800000000000003</v>
       </c>
-      <c r="J62" s="14">
+      <c r="J63" s="14">
         <v>0.34</v>
       </c>
-      <c r="K62" s="14">
+      <c r="K63" s="14">
         <f t="shared" si="4"/>
         <v>0.40800000000000003</v>
       </c>
-      <c r="L62" s="24">
+      <c r="L63" s="24">
         <f t="shared" si="5"/>
         <v>0.34</v>
       </c>
-      <c r="M62" s="16"/>
-      <c r="N62" s="15"/>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B63" t="s">
-        <v>268</v>
-      </c>
-      <c r="C63" t="s">
-        <v>351</v>
-      </c>
-      <c r="D63" t="s">
-        <v>186</v>
-      </c>
-      <c r="E63" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="G63" s="27">
+      <c r="M63" s="16"/>
+      <c r="N63" s="15"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A64" s="32"/>
+      <c r="B64" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64" t="s">
+        <v>346</v>
+      </c>
+      <c r="D64" t="s">
+        <v>185</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="G64">
         <v>1</v>
       </c>
-      <c r="I63" s="14">
+      <c r="I64" s="14">
         <f t="shared" si="3"/>
         <v>0.108</v>
       </c>
-      <c r="J63" s="14">
+      <c r="J64" s="14">
         <v>0.09</v>
       </c>
-      <c r="K63" s="14">
+      <c r="K64" s="14">
         <f t="shared" si="4"/>
         <v>0.108</v>
       </c>
-      <c r="L63" s="24">
+      <c r="L64" s="24">
         <f t="shared" si="5"/>
         <v>0.09</v>
       </c>
-      <c r="M63" s="16"/>
-      <c r="N63" s="15"/>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B64" t="s">
-        <v>268</v>
-      </c>
-      <c r="C64" t="s">
-        <v>354</v>
-      </c>
-      <c r="D64" t="s">
-        <v>186</v>
-      </c>
-      <c r="E64" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="G64" s="27">
+      <c r="M64" s="16"/>
+      <c r="N64" s="15"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>265</v>
+      </c>
+      <c r="C65" t="s">
+        <v>349</v>
+      </c>
+      <c r="D65" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="G65">
         <v>1</v>
       </c>
-      <c r="I64" s="14">
+      <c r="I65" s="14">
         <f t="shared" si="3"/>
         <v>0.69599999999999995</v>
       </c>
-      <c r="J64" s="14">
+      <c r="J65" s="14">
         <v>0.57999999999999996</v>
       </c>
-      <c r="K64" s="14">
+      <c r="K65" s="14">
         <f t="shared" si="4"/>
         <v>0.69599999999999995</v>
       </c>
-      <c r="L64" s="24">
+      <c r="L65" s="24">
         <f t="shared" si="5"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="M64" s="16"/>
-      <c r="N64" s="15"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B65" t="s">
-        <v>268</v>
-      </c>
-      <c r="C65" t="s">
-        <v>357</v>
-      </c>
-      <c r="D65" t="s">
-        <v>186</v>
-      </c>
-      <c r="E65" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="G65" s="27">
+      <c r="M65" s="16"/>
+      <c r="N65" s="15"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>265</v>
+      </c>
+      <c r="C66" t="s">
+        <v>352</v>
+      </c>
+      <c r="D66" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="G66">
         <v>1</v>
       </c>
-      <c r="I65" s="14">
+      <c r="I66" s="14">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
-      <c r="J65" s="14">
+      <c r="J66" s="14">
         <v>0.5</v>
       </c>
-      <c r="K65" s="14">
+      <c r="K66" s="14">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="L65" s="24">
+      <c r="L66" s="24">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="M65" s="16"/>
-      <c r="N65" s="15"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B66" t="s">
-        <v>268</v>
-      </c>
-      <c r="C66" t="s">
-        <v>359</v>
-      </c>
-      <c r="D66" t="s">
-        <v>186</v>
-      </c>
-      <c r="E66" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="G66" s="27">
-        <v>1</v>
-      </c>
-      <c r="I66" s="14">
-        <f t="shared" si="3"/>
-        <v>0.108</v>
-      </c>
-      <c r="J66" s="14">
-        <v>0.09</v>
-      </c>
-      <c r="K66" s="14">
-        <f t="shared" si="4"/>
-        <v>0.108</v>
-      </c>
-      <c r="L66" s="24">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
       <c r="M66" s="16"/>
       <c r="N66" s="15"/>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C67" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="31" t="s">
-        <v>360</v>
+        <v>185</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>236</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="G67" s="27">
+        <v>353</v>
+      </c>
+      <c r="G67">
         <v>1</v>
       </c>
       <c r="I67" s="14">
@@ -4107,22 +4076,22 @@
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C68" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
-      </c>
-      <c r="E68" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="F68" t="s">
-        <v>364</v>
-      </c>
-      <c r="G68" s="27">
-        <v>2</v>
+        <v>185</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
       </c>
       <c r="I68" s="14">
         <f t="shared" si="3"/>
@@ -4133,302 +4102,339 @@
       </c>
       <c r="K68" s="14">
         <f t="shared" si="4"/>
-        <v>0.216</v>
+        <v>0.108</v>
       </c>
       <c r="L68" s="24">
         <f t="shared" si="5"/>
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="M68" s="16"/>
       <c r="N68" s="15"/>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C69" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="D69" t="s">
-        <v>186</v>
-      </c>
-      <c r="E69" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="G69" s="27">
-        <v>3</v>
+        <v>185</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="F69" t="s">
+        <v>359</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
       </c>
       <c r="I69" s="14">
         <f t="shared" si="3"/>
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="J69" s="14">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K69" s="14">
         <f t="shared" si="4"/>
-        <v>0.36</v>
+        <v>0.216</v>
       </c>
       <c r="L69" s="24">
         <f t="shared" si="5"/>
-        <v>0.30000000000000004</v>
+        <v>0.18</v>
       </c>
       <c r="M69" s="16"/>
       <c r="N69" s="15"/>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C70" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
-      </c>
-      <c r="E70" s="31" t="s">
-        <v>370</v>
+        <v>185</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>361</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="G70" s="27">
-        <v>1</v>
+        <v>362</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
       </c>
       <c r="I70" s="14">
         <f t="shared" si="3"/>
-        <v>0.99599999999999989</v>
+        <v>0.12</v>
       </c>
       <c r="J70" s="14">
-        <v>0.83</v>
+        <v>0.1</v>
       </c>
       <c r="K70" s="14">
         <f t="shared" si="4"/>
-        <v>0.99599999999999989</v>
+        <v>0.36</v>
       </c>
       <c r="L70" s="24">
         <f t="shared" si="5"/>
-        <v>0.83</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="M70" s="16"/>
       <c r="N70" s="15"/>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C71" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D71" t="s">
-        <v>186</v>
-      </c>
-      <c r="E71" s="31" t="s">
-        <v>372</v>
+        <v>185</v>
+      </c>
+      <c r="E71" s="27" t="s">
+        <v>365</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="G71" s="27">
+        <v>366</v>
+      </c>
+      <c r="G71">
         <v>1</v>
       </c>
       <c r="I71" s="14">
         <f t="shared" si="3"/>
-        <v>7.032</v>
+        <v>0.99599999999999989</v>
       </c>
       <c r="J71" s="14">
-        <v>5.86</v>
+        <v>0.83</v>
       </c>
       <c r="K71" s="14">
         <f t="shared" si="4"/>
-        <v>7.032</v>
+        <v>0.99599999999999989</v>
       </c>
       <c r="L71" s="24">
         <f t="shared" si="5"/>
-        <v>5.86</v>
+        <v>0.83</v>
       </c>
       <c r="M71" s="16"/>
       <c r="N71" s="15"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C72" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="D72" t="s">
-        <v>186</v>
-      </c>
-      <c r="E72" s="31" t="s">
-        <v>375</v>
+        <v>185</v>
+      </c>
+      <c r="E72" s="27" t="s">
+        <v>367</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="G72" s="27">
+        <v>368</v>
+      </c>
+      <c r="G72">
         <v>1</v>
       </c>
       <c r="I72" s="14">
         <f t="shared" si="3"/>
-        <v>3.7199999999999998</v>
+        <v>7.032</v>
       </c>
       <c r="J72" s="14">
-        <v>3.1</v>
+        <v>5.86</v>
       </c>
       <c r="K72" s="14">
         <f t="shared" si="4"/>
-        <v>3.7199999999999998</v>
+        <v>7.032</v>
       </c>
       <c r="L72" s="24">
         <f t="shared" si="5"/>
-        <v>3.1</v>
+        <v>5.86</v>
       </c>
       <c r="M72" s="16"/>
       <c r="N72" s="15"/>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C73" t="s">
-        <v>177</v>
+        <v>372</v>
       </c>
       <c r="D73" t="s">
-        <v>378</v>
-      </c>
-      <c r="E73" s="31" t="s">
-        <v>379</v>
+        <v>185</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>370</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="G73" s="27">
-        <v>4</v>
+        <v>371</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
       </c>
       <c r="I73" s="14">
         <f t="shared" si="3"/>
-        <v>2.2559999999999998</v>
+        <v>3.7199999999999998</v>
       </c>
       <c r="J73" s="14">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="K73" s="14">
         <f t="shared" si="4"/>
-        <v>9.0239999999999991</v>
+        <v>3.7199999999999998</v>
       </c>
       <c r="L73" s="24">
         <f t="shared" si="5"/>
-        <v>7.52</v>
+        <v>3.1</v>
       </c>
       <c r="M73" s="16"/>
       <c r="N73" s="15"/>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C74" t="s">
-        <v>383</v>
+        <v>177</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
-      </c>
-      <c r="E74" s="31" t="s">
-        <v>381</v>
+        <v>373</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>374</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="G74" s="27">
-        <v>1</v>
+        <v>375</v>
+      </c>
+      <c r="G74">
+        <v>4</v>
       </c>
       <c r="I74" s="14">
         <f t="shared" si="3"/>
-        <v>3.492</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="J74" s="14">
-        <v>2.91</v>
+        <v>1.88</v>
       </c>
       <c r="K74" s="14">
         <f t="shared" si="4"/>
-        <v>3.492</v>
+        <v>9.0239999999999991</v>
       </c>
       <c r="L74" s="24">
         <f t="shared" si="5"/>
-        <v>2.91</v>
+        <v>7.52</v>
       </c>
       <c r="M74" s="16"/>
       <c r="N74" s="15"/>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="25"/>
-      <c r="J75" s="25"/>
-      <c r="K75" s="25"/>
-      <c r="L75" s="26"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12"/>
-      <c r="O75" s="2"/>
+      <c r="B75" t="s">
+        <v>265</v>
+      </c>
+      <c r="C75" t="s">
+        <v>378</v>
+      </c>
+      <c r="D75" t="s">
+        <v>185</v>
+      </c>
+      <c r="E75" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="I75" s="14">
+        <f t="shared" si="3"/>
+        <v>3.492</v>
+      </c>
+      <c r="J75" s="14">
+        <v>2.91</v>
+      </c>
+      <c r="K75" s="14">
+        <f t="shared" si="4"/>
+        <v>3.492</v>
+      </c>
+      <c r="L75" s="24">
+        <f t="shared" si="5"/>
+        <v>2.91</v>
+      </c>
+      <c r="M75" s="16"/>
+      <c r="N75" s="15"/>
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="D76" s="40"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="5">
-        <f>SUBTOTAL(9, K4:K75)</f>
-        <v>164.41200000000001</v>
-      </c>
-      <c r="L76" s="5">
-        <f>SUBTOTAL(9, L4:L75)</f>
-        <v>137.01000000000002</v>
-      </c>
-      <c r="M76" s="5"/>
-      <c r="N76" s="17">
-        <f>SUBTOTAL(9, N4:N75)</f>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="2"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="D77" s="30"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="5">
+        <f>SUBTOTAL(9, K4:K76)</f>
+        <v>164.50320000000002</v>
+      </c>
+      <c r="L77" s="5">
+        <f>SUBTOTAL(9, L4:L76)</f>
+        <v>137.08600000000001</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="17">
+        <f>SUBTOTAL(9, N4:N76)</f>
         <v>0</v>
       </c>
-      <c r="O76" s="10" t="s">
+      <c r="O77" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D80" s="11"/>
-    </row>
-    <row r="83" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F83" s="7"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
-    </row>
-    <row r="85" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="F85" s="7"/>
-    </row>
-    <row r="92" spans="6:14" x14ac:dyDescent="0.45">
-      <c r="H92" s="9"/>
+    <row r="81" spans="4:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D81" s="11"/>
+    </row>
+    <row r="84" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="F84" s="7"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+      <c r="N84" s="8"/>
+    </row>
+    <row r="86" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="F86" s="7"/>
+    </row>
+    <row r="93" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H93" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:O4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="F14" r:id="rId1" xr:uid="{071A4445-529C-4F26-89DD-8CCF197E0F5A}"/>
-    <hyperlink ref="F11" r:id="rId2" xr:uid="{773AF989-4834-4903-AA8A-946684195E9F}"/>
-    <hyperlink ref="F23" r:id="rId3" xr:uid="{3F80F80D-E07D-4A0F-915D-33579B79E009}"/>
-    <hyperlink ref="F24" r:id="rId4" xr:uid="{3324C705-C335-42F3-969A-C4EAD3EA1B69}"/>
-    <hyperlink ref="F25" r:id="rId5" xr:uid="{9841B8BF-59EF-47BB-A584-9C10791A2079}"/>
-    <hyperlink ref="F16" r:id="rId6" xr:uid="{EBA65772-6458-472F-AA5F-5636E6556499}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{AF630448-8F16-4823-B3EC-B153EC9F377E}"/>
-    <hyperlink ref="F31" r:id="rId8" xr:uid="{B1E9B6B1-C697-4F2D-A4EF-16B01FFB45B5}"/>
+    <hyperlink ref="F23" r:id="rId2" xr:uid="{3F80F80D-E07D-4A0F-915D-33579B79E009}"/>
+    <hyperlink ref="F24" r:id="rId3" xr:uid="{3324C705-C335-42F3-969A-C4EAD3EA1B69}"/>
+    <hyperlink ref="F25" r:id="rId4" xr:uid="{9841B8BF-59EF-47BB-A584-9C10791A2079}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{EBA65772-6458-472F-AA5F-5636E6556499}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{AF630448-8F16-4823-B3EC-B153EC9F377E}"/>
+    <hyperlink ref="F31" r:id="rId7" xr:uid="{B1E9B6B1-C697-4F2D-A4EF-16B01FFB45B5}"/>
+    <hyperlink ref="F64" r:id="rId8" xr:uid="{0CD72EC3-D9AA-42B9-B131-3F00716C4247}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>

--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Documents\Altium\3D-Display\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10330E0-592F-4F79-8972-688BCFB0D29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D9EF7B-A693-4C9C-A3F0-A45B282F0166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="387">
   <si>
     <t>Best.</t>
   </si>
@@ -587,6 +587,9 @@
     <t>RES 13.7K OHM 1/8W .1% SMD 0805</t>
   </si>
   <si>
+    <t>CAP 0.01uF 250V X7R 10% 0805 T/R</t>
+  </si>
+  <si>
     <t>CAP CER  0.1UF 25V X7R 0603</t>
   </si>
   <si>
@@ -728,6 +731,12 @@
     <t>CAP CER 0.01uF</t>
   </si>
   <si>
+    <t>603-C0805KKX7RYBB104</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4wwecmS</t>
+  </si>
+  <si>
     <t>CAP CER 2.2uF</t>
   </si>
   <si>
@@ -740,9 +749,6 @@
     <t xml:space="preserve">Res 100KΩ 0805 </t>
   </si>
   <si>
-    <t>https://mou.sr/3SR5DVs</t>
-  </si>
-  <si>
     <t>279-RQ73C2A100KBTD</t>
   </si>
   <si>
@@ -908,10 +914,10 @@
     <t>https://mou.sr/4vX50bj</t>
   </si>
   <si>
-    <t>https://mou.sr/4fgtJR1</t>
-  </si>
-  <si>
-    <t>https://mou.sr/4bgyqZO</t>
+    <t>81-GRM21BR61E106MA3L</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4vAmZUk</t>
   </si>
   <si>
     <t>810-CGA4J2X7R1C105KD</t>
@@ -1082,12 +1088,6 @@
     <t>Res 5k23 0805</t>
   </si>
   <si>
-    <t>603-RC0805FR-075K76L</t>
-  </si>
-  <si>
-    <t>https://mou.sr/3Teegtb</t>
-  </si>
-  <si>
     <t>Res 5k76 0805</t>
   </si>
   <si>
@@ -1115,12 +1115,6 @@
     <t>Res 13k7 0805</t>
   </si>
   <si>
-    <t>603-RC0805FR-07383RL</t>
-  </si>
-  <si>
-    <t>https://mou.sr/4h84vGX</t>
-  </si>
-  <si>
     <t>Res 383R 0805 Dickmann</t>
   </si>
   <si>
@@ -1178,19 +1172,43 @@
     <t>https://www.conrad.at/de/p/jst-einbau-stiftleiste-standard-ph-polzahl-gesamt-2-rastermass-2-mm-s2b-ph-k-s-lf-sn-1-st-740197.html?srsltid=AfmBOooo9BOmWD_uhxWb4a2mY14-Qu3-5fNR4kmU1FAuQtNaVtE351Be</t>
   </si>
   <si>
-    <t>71-WSHP28185L000FEA</t>
-  </si>
-  <si>
-    <t>https://mou.sr/4wXNu7h</t>
-  </si>
-  <si>
     <t>Strommesswiderstand</t>
   </si>
   <si>
-    <t>https://mou.sr/4hMsGJZ</t>
-  </si>
-  <si>
-    <t>80-C0805C106K8P</t>
+    <t>81-GRJ21BR61E106KE1L</t>
+  </si>
+  <si>
+    <t>Cap 10k</t>
+  </si>
+  <si>
+    <t>603-RT0805DRE1310KL</t>
+  </si>
+  <si>
+    <t>Res 47k</t>
+  </si>
+  <si>
+    <t>71-PTN0603E4701BST1</t>
+  </si>
+  <si>
+    <t>603-PE0805FRF070R005</t>
+  </si>
+  <si>
+    <t>667-ERJ-UP6F3830V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4hITEDg</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4y89GfG</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3Vezice</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3TmlrQE</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4ruSRJu</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1221,7 @@
     <numFmt numFmtId="166" formatCode="0.0\ &quot;kg&quot;"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0000\ &quot;€&quot;_-;\-* #,##0.0000\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1248,15 +1266,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1266,18 +1277,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1334,7 +1333,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1379,13 +1378,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -1669,8 +1661,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:O93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7.73046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
@@ -1681,8 +1673,8 @@
     <col min="8" max="8" width="12.73046875" customWidth="1"/>
     <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.59765625" customWidth="1"/>
     <col min="14" max="14" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="63.265625" bestFit="1" customWidth="1"/>
@@ -1690,7 +1682,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
@@ -1743,22 +1735,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="14">
         <f>J4*1.2</f>
@@ -1769,47 +1761,47 @@
       </c>
       <c r="K4" s="14">
         <f>I4*G4</f>
-        <v>0.312</v>
+        <v>0.624</v>
       </c>
       <c r="L4" s="24">
         <f>J4*G4</f>
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="M4" s="16"/>
       <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="I5" s="14">
-        <f t="shared" ref="I5:I28" si="0">J5*1.2</f>
+        <f t="shared" ref="I5:I27" si="0">J5*1.2</f>
         <v>0.84</v>
       </c>
       <c r="J5" s="14">
         <v>0.7</v>
       </c>
       <c r="K5" s="14">
-        <f t="shared" ref="K5:K28" si="1">I5*G5</f>
+        <f t="shared" ref="K5:K27" si="1">I5*G5</f>
         <v>6.72</v>
       </c>
       <c r="L5" s="24">
-        <f t="shared" ref="L5:L28" si="2">J5*G5</f>
+        <f t="shared" ref="L5:L27" si="2">J5*G5</f>
         <v>5.6</v>
       </c>
       <c r="M5" s="16"/>
@@ -1817,19 +1809,19 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="D6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="27" t="s">
+      <c r="F6" s="19" t="s">
         <v>224</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>223</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1853,23 +1845,22 @@
       <c r="N6" s="15"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A7" s="31"/>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="G7">
+        <v>215</v>
+      </c>
+      <c r="G7" s="31">
         <v>4</v>
       </c>
       <c r="I7" s="14">
@@ -1892,19 +1883,19 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1929,19 +1920,19 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1966,22 +1957,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I10" s="14">
         <f t="shared" si="0"/>
@@ -1992,46 +1983,67 @@
       </c>
       <c r="K10" s="14">
         <f t="shared" si="1"/>
-        <v>2.2559999999999998</v>
+        <v>5.64</v>
       </c>
       <c r="L10" s="24">
         <f t="shared" si="2"/>
-        <v>1.88</v>
+        <v>4.6999999999999993</v>
       </c>
       <c r="M10" s="16"/>
       <c r="N10" s="15"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="37"/>
+      <c r="B11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14">
+        <f t="shared" si="0"/>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.11</v>
+      </c>
+      <c r="K11" s="14">
+        <f t="shared" si="1"/>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="L11" s="24">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
       <c r="M11" s="16"/>
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="E12" s="27" t="s">
-        <v>184</v>
-      </c>
       <c r="F12" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -2056,19 +2068,19 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2093,19 +2105,19 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -2130,19 +2142,19 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -2167,19 +2179,19 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -2204,21 +2216,21 @@
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="G17">
+        <v>200</v>
+      </c>
+      <c r="G17" s="31">
         <v>2</v>
       </c>
       <c r="I17" s="14">
@@ -2241,19 +2253,19 @@
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2278,19 +2290,19 @@
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2315,19 +2327,19 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -2352,59 +2364,59 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>230</v>
+        <v>236</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>237</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v>0.49199999999999994</v>
+        <v>0.108</v>
       </c>
       <c r="J21" s="14">
-        <v>0.41</v>
+        <v>0.09</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" si="1"/>
-        <v>0.98399999999999987</v>
+        <v>0.108</v>
       </c>
       <c r="L21" s="24">
         <f t="shared" si="2"/>
-        <v>0.82</v>
+        <v>0.09</v>
       </c>
       <c r="M21" s="16"/>
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="G22" s="31">
+        <v>2</v>
       </c>
       <c r="I22" s="14">
         <f t="shared" si="0"/>
@@ -2415,33 +2427,33 @@
       </c>
       <c r="K22" s="14">
         <f t="shared" si="1"/>
-        <v>0.108</v>
+        <v>0.216</v>
       </c>
       <c r="L22" s="24">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="15"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>243</v>
+        <v>247</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>248</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" si="0"/>
@@ -2452,33 +2464,33 @@
       </c>
       <c r="K23" s="14">
         <f t="shared" si="1"/>
-        <v>0.108</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="L23" s="24">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>0.72</v>
       </c>
       <c r="M23" s="16"/>
       <c r="N23" s="15"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G24">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I24" s="14">
         <f t="shared" si="0"/>
@@ -2489,1542 +2501,1561 @@
       </c>
       <c r="K24" s="14">
         <f t="shared" si="1"/>
-        <v>0.86399999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="L24" s="24">
         <f t="shared" si="2"/>
-        <v>0.72</v>
+        <v>0.09</v>
       </c>
       <c r="M24" s="16"/>
       <c r="N24" s="15"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>237</v>
+        <v>195</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>196</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="I25" s="14">
         <f t="shared" si="0"/>
-        <v>0.108</v>
+        <v>6.48</v>
       </c>
       <c r="J25" s="14">
-        <v>0.09</v>
+        <v>5.4</v>
       </c>
       <c r="K25" s="14">
         <f t="shared" si="1"/>
-        <v>0.108</v>
+        <v>6.48</v>
       </c>
       <c r="L25" s="24">
         <f t="shared" si="2"/>
-        <v>0.09</v>
+        <v>5.4</v>
       </c>
       <c r="M25" s="16"/>
       <c r="N25" s="15"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>261</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>193</v>
+        <v>263</v>
+      </c>
+      <c r="C26" t="s">
+        <v>242</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="I26" s="14">
         <f t="shared" si="0"/>
-        <v>6.48</v>
+        <v>3.1799999999999997</v>
       </c>
       <c r="J26" s="14">
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="K26" s="14">
         <f t="shared" si="1"/>
-        <v>6.48</v>
+        <v>3.1799999999999997</v>
       </c>
       <c r="L26" s="24">
         <f t="shared" si="2"/>
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="M26" s="16"/>
       <c r="N26" s="15"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C27" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="I27" s="14">
         <f t="shared" si="0"/>
-        <v>3.1799999999999997</v>
-      </c>
-      <c r="J27" s="14">
-        <v>2.65</v>
+        <v>0.192</v>
+      </c>
+      <c r="J27" s="24">
+        <v>0.16</v>
       </c>
       <c r="K27" s="14">
         <f t="shared" si="1"/>
-        <v>3.1799999999999997</v>
+        <v>9.2160000000000011</v>
       </c>
       <c r="L27" s="24">
         <f t="shared" si="2"/>
-        <v>2.65</v>
+        <v>7.68</v>
       </c>
       <c r="M27" s="16"/>
       <c r="N27" s="15"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G28">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="I28" s="14">
-        <f t="shared" si="0"/>
-        <v>0.192</v>
+        <f>J28*1.2</f>
+        <v>2.1</v>
       </c>
       <c r="J28" s="24">
-        <v>0.16</v>
+        <v>1.75</v>
       </c>
       <c r="K28" s="14">
-        <f t="shared" si="1"/>
-        <v>9.2160000000000011</v>
+        <f>I28*G28</f>
+        <v>2.1</v>
       </c>
       <c r="L28" s="24">
-        <f t="shared" si="2"/>
-        <v>7.68</v>
+        <f>J28*G28</f>
+        <v>1.75</v>
       </c>
       <c r="M28" s="16"/>
       <c r="N28" s="15"/>
+      <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="14">
         <f>J29*1.2</f>
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="J29" s="24">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="14">
         <f>I29*G29</f>
-        <v>2.1</v>
+        <v>6.24</v>
       </c>
       <c r="L29" s="24">
         <f>J29*G29</f>
-        <v>1.75</v>
+        <v>5.2</v>
       </c>
       <c r="M29" s="16"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="28"/>
+      <c r="O29" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>254</v>
+        <v>186</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>256</v>
+        <v>262</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>260</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I30" s="14">
         <f>J30*1.2</f>
-        <v>3.12</v>
+        <v>1.92</v>
       </c>
       <c r="J30" s="24">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="K30" s="14">
         <f>I30*G30</f>
-        <v>6.24</v>
+        <v>19.2</v>
       </c>
       <c r="L30" s="24">
         <f>J30*G30</f>
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="M30" s="16"/>
       <c r="N30" s="15"/>
-      <c r="O30" t="s">
-        <v>257</v>
-      </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>258</v>
+        <v>269</v>
+      </c>
+      <c r="F31" t="s">
+        <v>270</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I31" s="14">
         <f>J31*1.2</f>
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="J31" s="24">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="K31" s="14">
         <f>I31*G31</f>
-        <v>19.2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="24">
         <f>J31*G31</f>
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="M31" s="16"/>
       <c r="N31" s="15"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="F32" t="s">
-        <v>268</v>
+        <v>271</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>272</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I32" s="14">
         <f>J32*1.2</f>
-        <v>3</v>
+        <v>0.68399999999999994</v>
       </c>
       <c r="J32" s="24">
-        <v>2.5</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="K32" s="14">
         <f>I32*G32</f>
-        <v>3</v>
+        <v>7.5239999999999991</v>
       </c>
       <c r="L32" s="24">
         <f>J32*G32</f>
-        <v>2.5</v>
+        <v>6.27</v>
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="15"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C33" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="G33">
-        <v>11</v>
+        <v>274</v>
+      </c>
+      <c r="G33" s="31">
+        <v>5</v>
       </c>
       <c r="I33" s="14">
-        <f>J33*1.2</f>
+        <f t="shared" ref="I33:I76" si="3">J33*1.2</f>
         <v>0.68399999999999994</v>
       </c>
       <c r="J33" s="24">
         <v>0.56999999999999995</v>
       </c>
       <c r="K33" s="14">
-        <f>I33*G33</f>
-        <v>7.5239999999999991</v>
+        <f t="shared" ref="K33:K76" si="4">I33*G33</f>
+        <v>3.42</v>
       </c>
       <c r="L33" s="24">
-        <f>J33*G33</f>
-        <v>6.27</v>
+        <f t="shared" ref="L33:L76" si="5">J33*G33</f>
+        <v>2.8499999999999996</v>
       </c>
       <c r="M33" s="16"/>
       <c r="N33" s="15"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C34" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>272</v>
+        <v>276</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>278</v>
       </c>
       <c r="G34">
         <v>2</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" ref="I34:I75" si="3">J34*1.2</f>
-        <v>0.68399999999999994</v>
+        <f t="shared" si="3"/>
+        <v>0.20400000000000001</v>
       </c>
       <c r="J34" s="24">
-        <v>0.56999999999999995</v>
+        <v>0.17</v>
       </c>
       <c r="K34" s="14">
-        <f t="shared" ref="K34:K75" si="4">I34*G34</f>
-        <v>1.3679999999999999</v>
+        <f t="shared" si="4"/>
+        <v>0.40800000000000003</v>
       </c>
       <c r="L34" s="24">
-        <f t="shared" ref="L34:L75" si="5">J34*G34</f>
-        <v>1.1399999999999999</v>
+        <f t="shared" si="5"/>
+        <v>0.34</v>
       </c>
       <c r="M34" s="16"/>
       <c r="N34" s="15"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>276</v>
+        <v>279</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>280</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35" s="14">
         <f t="shared" si="3"/>
-        <v>0.20400000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="J35" s="24">
-        <v>0.17</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K35" s="14">
         <f t="shared" si="4"/>
-        <v>0.40800000000000003</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="L35" s="24">
         <f t="shared" si="5"/>
-        <v>0.34</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M35" s="16"/>
       <c r="N35" s="15"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C36" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I36" s="14">
         <f t="shared" si="3"/>
-        <v>0.16800000000000001</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="J36" s="24">
-        <v>0.14000000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K36" s="14">
         <f t="shared" si="4"/>
-        <v>0.67200000000000004</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="L36" s="24">
         <f t="shared" si="5"/>
-        <v>0.56000000000000005</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="M36" s="16"/>
       <c r="N36" s="15"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C37" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" s="14">
         <f t="shared" si="3"/>
-        <v>0.33600000000000002</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="J37" s="24">
-        <v>0.28000000000000003</v>
+        <v>0.74</v>
       </c>
       <c r="K37" s="14">
         <f t="shared" si="4"/>
-        <v>0.33600000000000002</v>
+        <v>2.6640000000000001</v>
       </c>
       <c r="L37" s="24">
         <f t="shared" si="5"/>
-        <v>0.28000000000000003</v>
+        <v>2.2199999999999998</v>
       </c>
       <c r="M37" s="16"/>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G38">
         <v>3</v>
       </c>
       <c r="I38" s="14">
         <f t="shared" si="3"/>
-        <v>0.88800000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="J38" s="24">
-        <v>0.74</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K38" s="14">
         <f t="shared" si="4"/>
-        <v>2.6640000000000001</v>
+        <v>0.504</v>
       </c>
       <c r="L38" s="24">
         <f t="shared" si="5"/>
-        <v>2.2199999999999998</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="M38" s="16"/>
       <c r="N38" s="15"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>249</v>
+        <v>267</v>
+      </c>
+      <c r="C39" t="s">
+        <v>292</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>286</v>
+        <v>290</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>291</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="I39" s="14">
         <f t="shared" si="3"/>
-        <v>0.156</v>
+        <v>0.40800000000000003</v>
       </c>
       <c r="J39" s="24">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="K39" s="14">
         <f t="shared" si="4"/>
-        <v>0.312</v>
+        <v>0.81600000000000006</v>
       </c>
       <c r="L39" s="24">
         <f t="shared" si="5"/>
-        <v>0.26</v>
+        <v>0.68</v>
       </c>
       <c r="M39" s="16"/>
       <c r="N39" s="15"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A40" s="31"/>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C40" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>380</v>
+        <v>293</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40" s="14">
         <f t="shared" si="3"/>
-        <v>0.20639999999999997</v>
-      </c>
-      <c r="J40" s="24">
-        <v>0.17199999999999999</v>
+        <v>3.7199999999999998</v>
+      </c>
+      <c r="J40" s="14">
+        <v>3.1</v>
       </c>
       <c r="K40" s="14">
         <f t="shared" si="4"/>
-        <v>0.61919999999999997</v>
+        <v>3.7199999999999998</v>
       </c>
       <c r="L40" s="24">
         <f t="shared" si="5"/>
-        <v>0.51600000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="M40" s="16"/>
       <c r="N40" s="15"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A41" s="38"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="37"/>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" t="s">
+        <v>298</v>
+      </c>
+      <c r="D41" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="I41" s="14">
+        <f t="shared" si="3"/>
+        <v>1.728</v>
+      </c>
+      <c r="J41" s="14">
+        <v>1.44</v>
+      </c>
+      <c r="K41" s="14">
+        <f t="shared" si="4"/>
+        <v>1.728</v>
+      </c>
+      <c r="L41" s="24">
+        <f t="shared" si="5"/>
+        <v>1.44</v>
+      </c>
       <c r="M41" s="16"/>
       <c r="N41" s="15"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>301</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>228</v>
+        <v>299</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="G42">
         <v>2</v>
       </c>
       <c r="I42" s="14">
         <f t="shared" si="3"/>
-        <v>1.1279999999999999</v>
-      </c>
-      <c r="J42" s="24">
-        <v>0.94</v>
+        <v>0.42</v>
+      </c>
+      <c r="J42" s="14">
+        <v>0.35</v>
       </c>
       <c r="K42" s="14">
         <f t="shared" si="4"/>
-        <v>2.2559999999999998</v>
+        <v>0.84</v>
       </c>
       <c r="L42" s="24">
         <f t="shared" si="5"/>
-        <v>1.88</v>
+        <v>0.7</v>
       </c>
       <c r="M42" s="16"/>
       <c r="N42" s="15"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C43" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>288</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>289</v>
+        <v>302</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>304</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="14">
         <f t="shared" si="3"/>
-        <v>0.40800000000000003</v>
-      </c>
-      <c r="J43" s="24">
-        <v>0.34</v>
+        <v>6.3119999999999994</v>
+      </c>
+      <c r="J43" s="14">
+        <v>5.26</v>
       </c>
       <c r="K43" s="14">
         <f t="shared" si="4"/>
-        <v>0.81600000000000006</v>
+        <v>6.3119999999999994</v>
       </c>
       <c r="L43" s="24">
         <f t="shared" si="5"/>
-        <v>0.68</v>
+        <v>5.26</v>
       </c>
       <c r="M43" s="16"/>
       <c r="N43" s="15"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C44" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="I44" s="14">
         <f t="shared" si="3"/>
-        <v>3.7199999999999998</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="J44" s="14">
-        <v>3.1</v>
+        <v>0.59</v>
       </c>
       <c r="K44" s="14">
         <f t="shared" si="4"/>
-        <v>3.7199999999999998</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="L44" s="24">
         <f t="shared" si="5"/>
-        <v>3.1</v>
+        <v>0.59</v>
       </c>
       <c r="M44" s="16"/>
       <c r="N44" s="15"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C45" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D45" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>294</v>
+        <v>221</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="I45" s="14">
         <f t="shared" si="3"/>
-        <v>1.728</v>
+        <v>0.72</v>
       </c>
       <c r="J45" s="14">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="K45" s="14">
         <f t="shared" si="4"/>
-        <v>1.728</v>
+        <v>0.72</v>
       </c>
       <c r="L45" s="24">
         <f t="shared" si="5"/>
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="M45" s="16"/>
       <c r="N45" s="15"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C46" t="s">
-        <v>299</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>297</v>
+        <v>252</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="G46">
         <v>2</v>
       </c>
       <c r="I46" s="14">
         <f t="shared" si="3"/>
-        <v>0.42</v>
+        <v>2.1</v>
       </c>
       <c r="J46" s="14">
-        <v>0.35</v>
+        <v>1.75</v>
       </c>
       <c r="K46" s="14">
         <f t="shared" si="4"/>
-        <v>0.84</v>
+        <v>4.2</v>
       </c>
       <c r="L46" s="24">
         <f t="shared" si="5"/>
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="M46" s="16"/>
       <c r="N46" s="15"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C47" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="I47" s="14">
         <f t="shared" si="3"/>
-        <v>6.3119999999999994</v>
+        <v>0.93599999999999994</v>
       </c>
       <c r="J47" s="14">
-        <v>5.26</v>
+        <v>0.78</v>
       </c>
       <c r="K47" s="14">
         <f t="shared" si="4"/>
-        <v>6.3119999999999994</v>
+        <v>0.93599999999999994</v>
       </c>
       <c r="L47" s="24">
         <f t="shared" si="5"/>
-        <v>5.26</v>
+        <v>0.78</v>
       </c>
       <c r="M47" s="16"/>
       <c r="N47" s="15"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C48" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="I48" s="14">
         <f t="shared" si="3"/>
-        <v>0.70799999999999996</v>
+        <v>2.8919999999999999</v>
       </c>
       <c r="J48" s="14">
-        <v>0.59</v>
+        <v>2.41</v>
       </c>
       <c r="K48" s="14">
         <f t="shared" si="4"/>
-        <v>0.70799999999999996</v>
+        <v>2.8919999999999999</v>
       </c>
       <c r="L48" s="24">
         <f t="shared" si="5"/>
-        <v>0.59</v>
+        <v>2.41</v>
       </c>
       <c r="M48" s="16"/>
       <c r="N48" s="15"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C49" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>220</v>
+        <v>317</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="I49" s="14">
         <f t="shared" si="3"/>
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="J49" s="14">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="K49" s="14">
         <f t="shared" si="4"/>
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="L49" s="24">
         <f t="shared" si="5"/>
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="M49" s="16"/>
       <c r="N49" s="15"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C50" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="I50" s="14">
         <f t="shared" si="3"/>
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J50" s="14">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="K50" s="14">
         <f t="shared" si="4"/>
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="L50" s="24">
         <f t="shared" si="5"/>
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="M50" s="16"/>
       <c r="N50" s="15"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C51" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="I51" s="14">
         <f t="shared" si="3"/>
-        <v>0.93599999999999994</v>
+        <v>1.452</v>
       </c>
       <c r="J51" s="14">
-        <v>0.78</v>
+        <v>1.21</v>
       </c>
       <c r="K51" s="14">
         <f t="shared" si="4"/>
-        <v>0.93599999999999994</v>
+        <v>1.452</v>
       </c>
       <c r="L51" s="24">
         <f t="shared" si="5"/>
-        <v>0.78</v>
+        <v>1.21</v>
       </c>
       <c r="M51" s="16"/>
       <c r="N51" s="15"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C52" t="s">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="14">
         <f t="shared" si="3"/>
-        <v>2.8919999999999999</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="J52" s="14">
-        <v>2.41</v>
+        <v>0.94</v>
       </c>
       <c r="K52" s="14">
         <f t="shared" si="4"/>
-        <v>2.8919999999999999</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="L52" s="24">
         <f t="shared" si="5"/>
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
       <c r="M52" s="16"/>
       <c r="N52" s="15"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C53" t="s">
-        <v>317</v>
+        <v>232</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I53" s="14">
         <f t="shared" si="3"/>
-        <v>0.54</v>
+        <v>0.49199999999999994</v>
       </c>
       <c r="J53" s="14">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="K53" s="14">
         <f t="shared" si="4"/>
-        <v>0.54</v>
+        <v>2.4599999999999995</v>
       </c>
       <c r="L53" s="24">
         <f t="shared" si="5"/>
-        <v>0.45</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="M53" s="16"/>
       <c r="N53" s="15"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C54" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="I54" s="14">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="J54" s="14">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="K54" s="14">
         <f t="shared" si="4"/>
-        <v>0.6</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="L54" s="24">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M54" s="16"/>
       <c r="N54" s="15"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C55" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>321</v>
+        <v>236</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="I55" s="14">
         <f t="shared" si="3"/>
-        <v>1.452</v>
+        <v>0.108</v>
       </c>
       <c r="J55" s="14">
-        <v>1.21</v>
+        <v>0.09</v>
       </c>
       <c r="K55" s="14">
         <f t="shared" si="4"/>
-        <v>1.452</v>
+        <v>0.108</v>
       </c>
       <c r="L55" s="24">
         <f t="shared" si="5"/>
-        <v>1.21</v>
+        <v>0.09</v>
       </c>
       <c r="M55" s="16"/>
       <c r="N55" s="15"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>336</v>
       </c>
       <c r="D56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="G56">
         <v>2</v>
       </c>
       <c r="I56" s="14">
         <f t="shared" si="3"/>
-        <v>1.1279999999999999</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="J56" s="14">
-        <v>0.94</v>
+        <v>0.11</v>
       </c>
       <c r="K56" s="14">
         <f t="shared" si="4"/>
-        <v>2.2559999999999998</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L56" s="24">
         <f t="shared" si="5"/>
-        <v>1.88</v>
+        <v>0.22</v>
       </c>
       <c r="M56" s="16"/>
       <c r="N56" s="15"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C57" t="s">
-        <v>229</v>
+        <v>339</v>
       </c>
       <c r="D57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>231</v>
+        <v>337</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="G57">
         <v>3</v>
       </c>
       <c r="I57" s="14">
         <f t="shared" si="3"/>
-        <v>0.49199999999999994</v>
+        <v>0.108</v>
       </c>
       <c r="J57" s="14">
-        <v>0.41</v>
+        <v>0.09</v>
       </c>
       <c r="K57" s="14">
         <f t="shared" si="4"/>
-        <v>1.4759999999999998</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="L57" s="24">
         <f t="shared" si="5"/>
-        <v>1.23</v>
+        <v>0.27</v>
       </c>
       <c r="M57" s="16"/>
       <c r="N57" s="15"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C58" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E58" s="27" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" s="14">
         <f t="shared" si="3"/>
-        <v>0.27600000000000002</v>
+        <v>0.12</v>
       </c>
       <c r="J58" s="14">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="K58" s="14">
         <f t="shared" si="4"/>
-        <v>0.55200000000000005</v>
+        <v>0.12</v>
       </c>
       <c r="L58" s="24">
         <f t="shared" si="5"/>
-        <v>0.46</v>
+        <v>0.1</v>
       </c>
       <c r="M58" s="16"/>
       <c r="N58" s="15"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C59" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>234</v>
+        <v>343</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="I59" s="14">
         <f t="shared" si="3"/>
-        <v>0.108</v>
+        <v>0.40800000000000003</v>
       </c>
       <c r="J59" s="14">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="K59" s="14">
         <f t="shared" si="4"/>
-        <v>0.108</v>
+        <v>0.40800000000000003</v>
       </c>
       <c r="L59" s="24">
         <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="M59" s="16"/>
       <c r="N59" s="15"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C60" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E60" s="27" t="s">
-        <v>332</v>
+        <v>381</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>333</v>
+        <v>382</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="14">
         <f t="shared" si="3"/>
-        <v>0.13200000000000001</v>
+        <v>0.30959999999999999</v>
       </c>
       <c r="J60" s="14">
-        <v>0.11</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="K60" s="14">
         <f t="shared" si="4"/>
-        <v>0.26400000000000001</v>
+        <v>0.30959999999999999</v>
       </c>
       <c r="L60" s="24">
         <f t="shared" si="5"/>
-        <v>0.22</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="M60" s="16"/>
       <c r="N60" s="15"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C61" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="I61" s="14">
         <f t="shared" si="3"/>
-        <v>0.108</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="J61" s="14">
-        <v>0.09</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="K61" s="14">
         <f t="shared" si="4"/>
-        <v>0.108</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="L61" s="24">
         <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M61" s="16"/>
       <c r="N61" s="15"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C62" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" s="27" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="I62" s="14">
         <f t="shared" si="3"/>
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="J62" s="14">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="K62" s="14">
         <f t="shared" si="4"/>
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="L62" s="24">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="M62" s="16"/>
       <c r="N62" s="15"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C63" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D63" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>341</v>
+        <v>238</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="I63" s="14">
         <f t="shared" si="3"/>
-        <v>0.40800000000000003</v>
+        <v>0.108</v>
       </c>
       <c r="J63" s="14">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="K63" s="14">
         <f t="shared" si="4"/>
-        <v>0.40800000000000003</v>
+        <v>0.108</v>
       </c>
       <c r="L63" s="24">
         <f t="shared" si="5"/>
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="M63" s="16"/>
       <c r="N63" s="15"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A64" s="32"/>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C64" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" s="27" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="14">
         <f t="shared" si="3"/>
-        <v>0.108</v>
+        <v>0.186</v>
       </c>
       <c r="J64" s="14">
-        <v>0.09</v>
+        <v>0.155</v>
       </c>
       <c r="K64" s="14">
         <f t="shared" si="4"/>
-        <v>0.108</v>
+        <v>0.372</v>
       </c>
       <c r="L64" s="24">
         <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>0.31</v>
       </c>
       <c r="M64" s="16"/>
       <c r="N64" s="15"/>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>347</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>348</v>
+        <v>356</v>
+      </c>
+      <c r="F65" t="s">
+        <v>357</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" s="14">
         <f t="shared" si="3"/>
-        <v>0.69599999999999995</v>
+        <v>0.108</v>
       </c>
       <c r="J65" s="14">
-        <v>0.57999999999999996</v>
+        <v>0.09</v>
       </c>
       <c r="K65" s="14">
         <f t="shared" si="4"/>
-        <v>0.69599999999999995</v>
+        <v>0.216</v>
       </c>
       <c r="L65" s="24">
         <f t="shared" si="5"/>
-        <v>0.57999999999999996</v>
+        <v>0.18</v>
       </c>
       <c r="M65" s="16"/>
       <c r="N65" s="15"/>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C66" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I66" s="14">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="J66" s="14">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="K66" s="14">
         <f t="shared" si="4"/>
@@ -4039,418 +4070,412 @@
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C67" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="I67" s="14">
         <f t="shared" si="3"/>
-        <v>0.108</v>
+        <v>0.99599999999999989</v>
       </c>
       <c r="J67" s="14">
-        <v>0.09</v>
+        <v>0.83</v>
       </c>
       <c r="K67" s="14">
         <f t="shared" si="4"/>
-        <v>0.108</v>
+        <v>0.99599999999999989</v>
       </c>
       <c r="L67" s="24">
         <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>0.83</v>
       </c>
       <c r="M67" s="16"/>
       <c r="N67" s="15"/>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C68" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E68" s="27" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="I68" s="14">
         <f t="shared" si="3"/>
-        <v>0.108</v>
+        <v>7.032</v>
       </c>
       <c r="J68" s="14">
-        <v>0.09</v>
+        <v>5.86</v>
       </c>
       <c r="K68" s="14">
         <f t="shared" si="4"/>
-        <v>0.108</v>
+        <v>7.032</v>
       </c>
       <c r="L68" s="24">
         <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>5.86</v>
       </c>
       <c r="M68" s="16"/>
       <c r="N68" s="15"/>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C69" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" s="27" t="s">
-        <v>358</v>
-      </c>
-      <c r="F69" t="s">
-        <v>359</v>
+        <v>368</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>369</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69" s="14">
         <f t="shared" si="3"/>
-        <v>0.108</v>
+        <v>3.7199999999999998</v>
       </c>
       <c r="J69" s="14">
-        <v>0.09</v>
+        <v>3.1</v>
       </c>
       <c r="K69" s="14">
         <f t="shared" si="4"/>
-        <v>0.216</v>
+        <v>3.7199999999999998</v>
       </c>
       <c r="L69" s="24">
         <f t="shared" si="5"/>
-        <v>0.18</v>
+        <v>3.1</v>
       </c>
       <c r="M69" s="16"/>
       <c r="N69" s="15"/>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C70" t="s">
-        <v>363</v>
+        <v>177</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>371</v>
       </c>
       <c r="E70" s="27" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" s="14">
         <f t="shared" si="3"/>
-        <v>0.12</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="J70" s="14">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="K70" s="14">
         <f t="shared" si="4"/>
-        <v>0.36</v>
+        <v>9.0239999999999991</v>
       </c>
       <c r="L70" s="24">
         <f t="shared" si="5"/>
-        <v>0.30000000000000004</v>
+        <v>7.52</v>
       </c>
       <c r="M70" s="16"/>
       <c r="N70" s="15"/>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C71" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D71" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E71" s="27" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="I71" s="14">
         <f t="shared" si="3"/>
-        <v>0.99599999999999989</v>
+        <v>1.296</v>
       </c>
       <c r="J71" s="14">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="K71" s="14">
         <f t="shared" si="4"/>
-        <v>0.99599999999999989</v>
+        <v>1.296</v>
       </c>
       <c r="L71" s="24">
         <f t="shared" si="5"/>
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="M71" s="16"/>
       <c r="N71" s="15"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C72" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="D72" t="s">
-        <v>185</v>
-      </c>
-      <c r="E72" s="27" t="s">
-        <v>367</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>368</v>
+        <v>186</v>
+      </c>
+      <c r="E72" t="s">
+        <v>377</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>385</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I72" s="14">
         <f t="shared" si="3"/>
-        <v>7.032</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J72" s="14">
-        <v>5.86</v>
+        <v>0.12</v>
       </c>
       <c r="K72" s="14">
         <f t="shared" si="4"/>
-        <v>7.032</v>
+        <v>0.86399999999999988</v>
       </c>
       <c r="L72" s="24">
         <f t="shared" si="5"/>
-        <v>5.86</v>
+        <v>0.72</v>
       </c>
       <c r="M72" s="16"/>
       <c r="N72" s="15"/>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C73" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="D73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" s="27" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="I73" s="14">
         <f t="shared" si="3"/>
-        <v>3.7199999999999998</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J73" s="14">
-        <v>3.1</v>
+        <v>0.12</v>
       </c>
       <c r="K73" s="14">
         <f t="shared" si="4"/>
-        <v>3.7199999999999998</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="L73" s="24">
         <f t="shared" si="5"/>
-        <v>3.1</v>
+        <v>0.12</v>
       </c>
       <c r="M73" s="16"/>
       <c r="N73" s="15"/>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B74" t="s">
-        <v>265</v>
-      </c>
-      <c r="C74" t="s">
-        <v>177</v>
-      </c>
-      <c r="D74" t="s">
-        <v>373</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>374</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="G74">
-        <v>4</v>
-      </c>
+      <c r="E74" s="27"/>
+      <c r="F74" s="19"/>
       <c r="I74" s="14">
         <f t="shared" si="3"/>
-        <v>2.2559999999999998</v>
-      </c>
-      <c r="J74" s="14">
-        <v>1.88</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J74" s="14"/>
       <c r="K74" s="14">
         <f t="shared" si="4"/>
-        <v>9.0239999999999991</v>
+        <v>0</v>
       </c>
       <c r="L74" s="24">
         <f t="shared" si="5"/>
-        <v>7.52</v>
+        <v>0</v>
       </c>
       <c r="M74" s="16"/>
       <c r="N74" s="15"/>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B75" t="s">
-        <v>265</v>
-      </c>
-      <c r="C75" t="s">
-        <v>378</v>
-      </c>
-      <c r="D75" t="s">
-        <v>185</v>
-      </c>
-      <c r="E75" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="F75" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
+      <c r="E75" s="27"/>
+      <c r="F75" s="19"/>
       <c r="I75" s="14">
         <f t="shared" si="3"/>
-        <v>3.492</v>
-      </c>
-      <c r="J75" s="14">
-        <v>2.91</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J75" s="14"/>
       <c r="K75" s="14">
         <f t="shared" si="4"/>
-        <v>3.492</v>
+        <v>0</v>
       </c>
       <c r="L75" s="24">
         <f t="shared" si="5"/>
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="M75" s="16"/>
       <c r="N75" s="15"/>
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="25"/>
-      <c r="J76" s="25"/>
-      <c r="K76" s="25"/>
-      <c r="L76" s="26"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12"/>
-      <c r="O76" s="2"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="19"/>
+      <c r="I76" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J76" s="14"/>
+      <c r="K76" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L76" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M76" s="16"/>
+      <c r="N76" s="15"/>
     </row>
     <row r="77" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="D77" s="30"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="5">
-        <f>SUBTOTAL(9, K4:K76)</f>
-        <v>164.50320000000002</v>
-      </c>
-      <c r="L77" s="5">
-        <f>SUBTOTAL(9, L4:L76)</f>
-        <v>137.08600000000001</v>
-      </c>
-      <c r="M77" s="5"/>
-      <c r="N77" s="17">
-        <f>SUBTOTAL(9, N4:N76)</f>
+      <c r="E77" s="27"/>
+      <c r="F77" s="19"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
+      <c r="L77" s="24"/>
+      <c r="M77" s="16"/>
+      <c r="N77" s="15"/>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
+      <c r="O78" s="2"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="D79" s="30"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="5">
+        <f>SUBTOTAL(9, K4:K78)</f>
+        <v>167.54159999999999</v>
+      </c>
+      <c r="L79" s="5">
+        <f>SUBTOTAL(9, L4:L78)</f>
+        <v>139.61800000000002</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="17">
+        <f>SUBTOTAL(9, N4:N78)</f>
         <v>0</v>
       </c>
-      <c r="O77" s="10" t="s">
+      <c r="O79" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="4:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D81" s="11"/>
-    </row>
-    <row r="84" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="F84" s="7"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
+    <row r="83" spans="4:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D83" s="11"/>
     </row>
     <row r="86" spans="4:14" x14ac:dyDescent="0.45">
       <c r="F86" s="7"/>
-    </row>
-    <row r="93" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="H93" s="9"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="8"/>
+    </row>
+    <row r="88" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="F88" s="7"/>
+    </row>
+    <row r="95" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H95" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:O4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="F14" r:id="rId1" xr:uid="{071A4445-529C-4F26-89DD-8CCF197E0F5A}"/>
-    <hyperlink ref="F23" r:id="rId2" xr:uid="{3F80F80D-E07D-4A0F-915D-33579B79E009}"/>
-    <hyperlink ref="F24" r:id="rId3" xr:uid="{3324C705-C335-42F3-969A-C4EAD3EA1B69}"/>
-    <hyperlink ref="F25" r:id="rId4" xr:uid="{9841B8BF-59EF-47BB-A584-9C10791A2079}"/>
-    <hyperlink ref="F16" r:id="rId5" xr:uid="{EBA65772-6458-472F-AA5F-5636E6556499}"/>
-    <hyperlink ref="F8" r:id="rId6" xr:uid="{AF630448-8F16-4823-B3EC-B153EC9F377E}"/>
-    <hyperlink ref="F31" r:id="rId7" xr:uid="{B1E9B6B1-C697-4F2D-A4EF-16B01FFB45B5}"/>
-    <hyperlink ref="F64" r:id="rId8" xr:uid="{0CD72EC3-D9AA-42B9-B131-3F00716C4247}"/>
+    <hyperlink ref="F11" r:id="rId2" xr:uid="{773AF989-4834-4903-AA8A-946684195E9F}"/>
+    <hyperlink ref="F22" r:id="rId3" xr:uid="{3F80F80D-E07D-4A0F-915D-33579B79E009}"/>
+    <hyperlink ref="F23" r:id="rId4" xr:uid="{3324C705-C335-42F3-969A-C4EAD3EA1B69}"/>
+    <hyperlink ref="F24" r:id="rId5" xr:uid="{9841B8BF-59EF-47BB-A584-9C10791A2079}"/>
+    <hyperlink ref="F16" r:id="rId6" xr:uid="{EBA65772-6458-472F-AA5F-5636E6556499}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{AF630448-8F16-4823-B3EC-B153EC9F377E}"/>
+    <hyperlink ref="F30" r:id="rId8" xr:uid="{B1E9B6B1-C697-4F2D-A4EF-16B01FFB45B5}"/>
+    <hyperlink ref="F38" r:id="rId9" xr:uid="{5B49022B-3171-45CC-AF94-147EB10E6CB7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:F47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="26.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55.73046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="71.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="71.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
@@ -5190,7 +5215,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Tabelle2"/>
   <dimension ref="B2:O27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7.73046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.265625" customWidth="1"/>
@@ -5201,8 +5226,8 @@
     <col min="8" max="8" width="12.73046875" customWidth="1"/>
     <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.59765625" customWidth="1"/>
     <col min="14" max="14" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="63.265625" bestFit="1" customWidth="1"/>
@@ -5527,7 +5552,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B3:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="6.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
